--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20140632</t>
-  </si>
-  <si>
-    <t>INDOMI NYMEK J/RD 84</t>
+    <t>20115362</t>
+  </si>
+  <si>
+    <t>CHUBA KRP BALADO 125</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,37 +28,28 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20138358</t>
-  </si>
-  <si>
-    <t>INDOMI NYEMK B/LDS80</t>
+    <t>RT,(E-1.5B)</t>
+  </si>
+  <si>
+    <t>20068906</t>
+  </si>
+  <si>
+    <t>FF SKM COKELAT 535G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20094283</t>
-  </si>
-  <si>
-    <t>INDOMILK KM PTH 535G</t>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20068905</t>
+  </si>
+  <si>
+    <t>FF SKM PUTIH 535G</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20120855</t>
-  </si>
-  <si>
-    <t>INDOMILK SWIS CHO535</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -451,13 +442,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -517,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -534,30 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>20115362</t>
-  </si>
-  <si>
-    <t>CHUBA KRP BALADO 125</t>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 5'S</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,28 +28,16 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1.5B)</t>
-  </si>
-  <si>
-    <t>20068906</t>
-  </si>
-  <si>
-    <t>FF SKM COKELAT 535G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP AYM BWG 5'S</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20068905</t>
-  </si>
-  <si>
-    <t>FF SKM PUTIH 535G</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -442,13 +430,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -508,27 +496,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t/>
   </si>
   <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 5'S</t>
+    <t>20114757</t>
+  </si>
+  <si>
+    <t>GURIBEE RMP.LAUT 65G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,16 +28,25 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20140674</t>
-  </si>
-  <si>
-    <t>SEDAAP AYM BWG 5'S</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20114756</t>
+  </si>
+  <si>
+    <t>GURIBEE BBQ BLDO 65G</t>
   </si>
   <si>
     <t>2</t>
+  </si>
+  <si>
+    <t>20130511</t>
+  </si>
+  <si>
+    <t>GURIBEE KEJU 65G</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -430,13 +439,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -496,6 +505,26 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20114757</t>
-  </si>
-  <si>
-    <t>GURIBEE RMP.LAUT 65G</t>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,22 +28,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20114756</t>
-  </si>
-  <si>
-    <t>GURIBEE BBQ BLDO 65G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20130511</t>
-  </si>
-  <si>
-    <t>GURIBEE KEJU 65G</t>
+    <t>20099297</t>
+  </si>
+  <si>
+    <t>SDAAP MIE SP.CHKN 81</t>
   </si>
   <si>
     <t>3</t>
@@ -445,7 +445,7 @@
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
   <si>
     <t/>
   </si>
   <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
+    <t>20119437</t>
+  </si>
+  <si>
+    <t>POTABEE BBG 115G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,25 +28,19 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20045611</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRNG CUP85</t>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20134456</t>
+  </si>
+  <si>
+    <t>JAPOTA SEAWEED 115G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20099297</t>
-  </si>
-  <si>
-    <t>SDAAP MIE SP.CHKN 81</t>
-  </si>
-  <si>
-    <t>3</t>
+    <t>RT,(E-14H)</t>
   </si>
 </sst>
 </file>
@@ -439,13 +433,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -505,27 +499,7 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20119437</t>
-  </si>
-  <si>
-    <t>POTABEE BBG 115G</t>
+    <t>20116675</t>
+  </si>
+  <si>
+    <t>CHTATO LITE NORI 115</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,19 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20134456</t>
-  </si>
-  <si>
-    <t>JAPOTA SEAWEED 115G</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20093109</t>
+  </si>
+  <si>
+    <t>KUSUKA ORIGINAL 180G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20000516</t>
+  </si>
+  <si>
+    <t>KUSUKA KRPK BBQ 180</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20093110</t>
+  </si>
+  <si>
+    <t>KUSUKA BALADO 180G</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -433,13 +451,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="13" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -499,6 +517,46 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>20116675</t>
-  </si>
-  <si>
-    <t>CHTATO LITE NORI 115</t>
+    <t>10023790</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE AYM BWG70</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,37 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20093109</t>
-  </si>
-  <si>
-    <t>KUSUKA ORIGINAL 180G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20114755</t>
+  </si>
+  <si>
+    <t>SDP MIE SPC.LAKSA 83</t>
+  </si>
+  <si>
+    <t>10023792</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE SOTO 76GR</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20000516</t>
-  </si>
-  <si>
-    <t>KUSUKA KRPK BBQ 180</t>
+    <t>20025418</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE KARI SP75</t>
+  </si>
+  <si>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>20093110</t>
-  </si>
-  <si>
-    <t>KUSUKA BALADO 180G</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
 </sst>
 </file>
@@ -451,13 +451,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -514,18 +514,18 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -534,18 +534,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -554,10 +554,30 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
   <si>
     <t/>
   </si>
   <si>
-    <t>10023790</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE AYM BWG70</t>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -29,36 +29,6 @@
   </si>
   <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20114755</t>
-  </si>
-  <si>
-    <t>SDP MIE SPC.LAKSA 83</t>
-  </si>
-  <si>
-    <t>10023792</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE SOTO 76GR</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20025418</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE KARI SP75</t>
-  </si>
-  <si>
-    <t>20045611</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRNG CUP85</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -451,11 +421,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -500,86 +470,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t/>
   </si>
   <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
+    <t>20045611</t>
+  </si>
+  <si>
+    <t>SEDAAP MI GRNG CUP85</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -29,6 +29,33 @@
   </si>
   <si>
     <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO CUP81</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20052391</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE K/S CUP81</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20099297</t>
+  </si>
+  <si>
+    <t>SDAAP MIE SP.CHKN 81</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -421,11 +448,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
@@ -470,6 +497,66 @@
         <v>5</v>
       </c>
     </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20045611</t>
-  </si>
-  <si>
-    <t>SEDAAP MI GRNG CUP85</t>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMNYES TKYO CHKN 84G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -31,31 +31,25 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20045610</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO CUP81</t>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMNYES HKTA CHKN 88G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20052391</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE K/S CUP81</t>
+    <t>20037153</t>
+  </si>
+  <si>
+    <t>KAKI3 PENYEGAR 500ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>20099297</t>
-  </si>
-  <si>
-    <t>SDAAP MIE SP.CHKN 81</t>
-  </si>
-  <si>
-    <t>4</t>
+    <t>RT,(E-4B)</t>
   </si>
 </sst>
 </file>
@@ -448,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -534,27 +528,7 @@
         <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
   <si>
     <t/>
   </si>
   <si>
-    <t>20141466</t>
-  </si>
-  <si>
-    <t>RMNYES TKYO CHKN 84G</t>
+    <t>20099679</t>
+  </si>
+  <si>
+    <t>LEMONILO MIE GRG 65G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -31,25 +31,40 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20141464</t>
-  </si>
-  <si>
-    <t>RMNYES HKTA CHKN 88G</t>
+    <t>20113972</t>
+  </si>
+  <si>
+    <t>LEMONILO PDS KOREA68</t>
+  </si>
+  <si>
+    <t>20069768</t>
+  </si>
+  <si>
+    <t>BIHUNKU SOTO SPS 55G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20037153</t>
-  </si>
-  <si>
-    <t>KAKI3 PENYEGAR 500ML</t>
+    <t>20141374</t>
+  </si>
+  <si>
+    <t>BIHUNKU BASO SAPI 50</t>
+  </si>
+  <si>
+    <t>10035852</t>
+  </si>
+  <si>
+    <t>BIHUNKU GRG SPCL 60G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
+    <t>20039494</t>
+  </si>
+  <si>
+    <t>BIHUNKU AYM BWG 55G</t>
   </si>
 </sst>
 </file>
@@ -442,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -505,7 +520,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -513,10 +528,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,10 +540,70 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t/>
   </si>
   <si>
-    <t>20099679</t>
-  </si>
-  <si>
-    <t>LEMONILO MIE GRG 65G</t>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,43 +28,34 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20085115</t>
+  </si>
+  <si>
+    <t>INDOMI GRNG ACEH 90G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20085462</t>
+  </si>
+  <si>
+    <t>INDOMIE SOTO LMNG 80</t>
+  </si>
+  <si>
+    <t>20096589</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE GRNG 5'S</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20113972</t>
-  </si>
-  <si>
-    <t>LEMONILO PDS KOREA68</t>
-  </si>
-  <si>
-    <t>20069768</t>
-  </si>
-  <si>
-    <t>BIHUNKU SOTO SPS 55G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20141374</t>
-  </si>
-  <si>
-    <t>BIHUNKU BASO SAPI 50</t>
-  </si>
-  <si>
-    <t>10035852</t>
-  </si>
-  <si>
-    <t>BIHUNKU GRG SPCL 60G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20039494</t>
-  </si>
-  <si>
-    <t>BIHUNKU AYM BWG 55G</t>
   </si>
 </sst>
 </file>
@@ -457,7 +448,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -520,7 +511,7 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>5</v>
@@ -528,10 +519,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -540,7 +531,7 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
@@ -560,50 +551,10 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,51 +11,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
   <si>
     <t/>
   </si>
   <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
+  </si>
+  <si>
+    <t>DU2AMKT</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>20019930</t>
   </si>
   <si>
     <t>INDOMIE GRG RNDANG91</t>
   </si>
   <si>
-    <t>DU2AMKT</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20085115</t>
-  </si>
-  <si>
-    <t>INDOMI GRNG ACEH 90G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20085462</t>
-  </si>
-  <si>
-    <t>INDOMIE SOTO LMNG 80</t>
-  </si>
-  <si>
-    <t>20096589</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE GRNG 5'S</t>
-  </si>
-  <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -448,7 +439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -531,30 +522,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
+    <t>20096590</t>
+  </si>
+  <si>
+    <t>SEDAAP MI STO 5x76 G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,25 +28,16 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140674</t>
+  </si>
+  <si>
+    <t>SEDAAP MI AYB 5x71 G</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
 </sst>
 </file>
@@ -439,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -508,26 +499,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
   <si>
     <t/>
   </si>
   <si>
-    <t>20096590</t>
-  </si>
-  <si>
-    <t>SEDAAP MI STO 5x76 G</t>
+    <t>10003800</t>
+  </si>
+  <si>
+    <t>INDOMI GR SP JUMB129</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,16 +28,46 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20130807</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDNG120</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>10003801</t>
+  </si>
+  <si>
+    <t>INDOMI JMB AYM PG127</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20083795</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT CHO 6X110</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20140674</t>
-  </si>
-  <si>
-    <t>SEDAAP MI AYB 5x71 G</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>20091183</t>
+  </si>
+  <si>
+    <t>F/FLAG UHT STR 6X110</t>
+  </si>
+  <si>
+    <t>5</t>
   </si>
 </sst>
 </file>
@@ -430,7 +460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -499,6 +529,66 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003800</t>
-  </si>
-  <si>
-    <t>INDOMI GR SP JUMB129</t>
+    <t>20067395</t>
+  </si>
+  <si>
+    <t>NISSIN GEKI.GRNG 118</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,46 +28,28 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20130807</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDNG120</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20139291</t>
+  </si>
+  <si>
+    <t>FLOATY SNACK BWNG 60</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>10003801</t>
-  </si>
-  <si>
-    <t>INDOMI JMB AYM PG127</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20140056</t>
+  </si>
+  <si>
+    <t>FLOATY TERSERAH 60G</t>
   </si>
   <si>
     <t>3</t>
-  </si>
-  <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20091183</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT STR 6X110</t>
-  </si>
-  <si>
-    <t>5</t>
   </si>
 </sst>
 </file>
@@ -460,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -526,15 +508,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -543,50 +525,10 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="12">
   <si>
     <t/>
   </si>
   <si>
-    <t>20067395</t>
-  </si>
-  <si>
-    <t>NISSIN GEKI.GRNG 118</t>
+    <t>10001094</t>
+  </si>
+  <si>
+    <t>CHITATO SAPI PGG 65G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,25 +28,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20139291</t>
-  </si>
-  <si>
-    <t>FLOATY SNACK BWNG 60</t>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20122264</t>
+  </si>
+  <si>
+    <t>CHITATO MI GORENG 65</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20140056</t>
-  </si>
-  <si>
-    <t>FLOATY TERSERAH 60G</t>
+    <t>20014506</t>
+  </si>
+  <si>
+    <t>CHITATO CHEESE SPR65</t>
   </si>
   <si>
     <t>3</t>
@@ -442,16 +439,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,8 +468,14 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>0</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -487,11 +491,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -507,16 +511,16 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -525,9 +529,9 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
   <si>
     <t/>
   </si>
   <si>
-    <t>10001094</t>
-  </si>
-  <si>
-    <t>CHITATO SAPI PGG 65G</t>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,25 +28,37 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20122264</t>
-  </si>
-  <si>
-    <t>CHITATO MI GORENG 65</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20014506</t>
-  </si>
-  <si>
-    <t>CHITATO CHEESE SPR65</t>
+    <t>20019930</t>
+  </si>
+  <si>
+    <t>INDOMIE GRG RNDANG91</t>
   </si>
   <si>
     <t>3</t>
+  </si>
+  <si>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAAP MIE STO CUP81</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -439,17 +451,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="5" width="3" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -468,14 +479,8 @@
       <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -491,11 +496,11 @@
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -511,11 +516,11 @@
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -531,8 +536,28 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
   <si>
     <t/>
   </si>
   <si>
-    <t>10003517</t>
-  </si>
-  <si>
-    <t>INDOMI GORENG SPC 80</t>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MH MAITOS S.BLDO 120</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,37 +28,16 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>10000185</t>
-  </si>
-  <si>
-    <t>INDOMI KARI AYAM 72G</t>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20072195</t>
+  </si>
+  <si>
+    <t>MH MAITOS JG.BBQ 120</t>
   </si>
   <si>
     <t>2</t>
-  </si>
-  <si>
-    <t>20019930</t>
-  </si>
-  <si>
-    <t>INDOMIE GRG RNDANG91</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20045610</t>
-  </si>
-  <si>
-    <t>SEDAAP MIE STO CUP81</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -451,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -520,46 +499,6 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MH MAITOS S.BLDO 120</t>
+    <t>10003517</t>
+  </si>
+  <si>
+    <t>INDOMI GORENG SPC 80</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,13 +28,13 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20072195</t>
-  </si>
-  <si>
-    <t>MH MAITOS JG.BBQ 120</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10000185</t>
+  </si>
+  <si>
+    <t>INDOMI KARI AYAM 72G</t>
   </si>
   <si>
     <t>2</t>
